--- a/E/R099N.xlsx
+++ b/E/R099N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
   <si>
     <t/>
   </si>
@@ -34,28 +34,19 @@
     <t>RT,(E-7H)</t>
   </si>
   <si>
-    <t>20083462</t>
-  </si>
-  <si>
-    <t>SG PAHA&amp;DADA P/M 450</t>
+    <t>20087415</t>
+  </si>
+  <si>
+    <t>SG CHKN.NUG ALPH 200</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>16</t>
+    <t>22</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20087415</t>
-  </si>
-  <si>
-    <t>SG CHKN.NUG ALPH 200</t>
-  </si>
-  <si>
-    <t>22</t>
   </si>
   <si>
     <t>20093522</t>
@@ -457,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -548,26 +539,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/R099N.xlsx
+++ b/E/R099N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
@@ -32,30 +32,6 @@
   </si>
   <si>
     <t>RT,(E-7H)</t>
-  </si>
-  <si>
-    <t>20087415</t>
-  </si>
-  <si>
-    <t>SG CHKN.NUG ALPH 200</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20093522</t>
-  </si>
-  <si>
-    <t>SG SPCY CHKN STRP250</t>
-  </si>
-  <si>
-    <t>24</t>
   </si>
 </sst>
 </file>
@@ -448,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -499,46 +475,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/R099N.xlsx
+++ b/E/R099N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
   <si>
     <t/>
   </si>
@@ -424,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -432,10 +432,11 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -454,8 +455,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -471,7 +478,7 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/E/R099N.xlsx
+++ b/E/R099N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
   <si>
     <t/>
   </si>
@@ -424,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -432,11 +432,10 @@
     <col min="3" max="3" width="7" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -455,14 +454,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -478,7 +471,7 @@
       <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
